--- a/tests/TC-05/results/teacher_timetables_even.xlsx
+++ b/tests/TC-05/results/teacher_timetables_even.xlsx
@@ -616,7 +616,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>CS402 LEC
@@ -624,34 +630,28 @@
 Room: 102</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -669,10 +669,34 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -681,27 +705,9 @@
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
     </row>
@@ -713,61 +719,19 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
@@ -783,10 +747,34 @@
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
@@ -815,26 +803,32 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>CS401 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>CS401 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>CS401 TUT
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>CS401 TUT
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>CS401 TUT
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>

--- a/tests/TC-05/results/teacher_timetables_even.xlsx
+++ b/tests/TC-05/results/teacher_timetables_even.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-        <bgColor rgb="00BBDEFB"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
   </fills>
@@ -616,42 +616,36 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>CS401 TUT
 (CSE_4_B)
 Room: 102</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>CS401 TUT
 (CSE_4_B)
 Room: 102</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>CS401 TUT
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -669,34 +663,10 @@
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
@@ -718,8 +688,20 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
@@ -745,36 +727,24 @@
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
@@ -782,9 +752,27 @@
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
@@ -808,29 +796,29 @@
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>CS401 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>CS401 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>CS401 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
